--- a/code/src/Q2/outputs/表2_问题2调度结果.xlsx
+++ b/code/src/Q2/outputs/表2_问题2调度结果.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表2_调度明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="表2_调度明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="汇总" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,16 +18,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +35,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -46,21 +43,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -426,36 +414,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>设备编号</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>起始时间</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>结束时间</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>持续工作时间(s)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>工序编号</t>
         </is>
@@ -472,12 +460,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>00:03:20</t>
+          <t>01:42:05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>00:21:20</t>
+          <t>02:00:05</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -500,12 +488,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>00:03:20</t>
+          <t>01:42:05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>00:21:20</t>
+          <t>02:00:05</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -528,12 +516,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>00:03:20</t>
+          <t>01:42:05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>00:21:20</t>
+          <t>02:00:05</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -556,12 +544,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>00:03:20</t>
+          <t>01:42:05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>00:21:20</t>
+          <t>02:00:05</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -584,12 +572,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>00:03:20</t>
+          <t>01:42:05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>00:21:20</t>
+          <t>02:00:05</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -612,12 +600,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>00:03:20</t>
+          <t>01:42:05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00:21:20</t>
+          <t>02:00:05</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -640,12 +628,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>00:03:20</t>
+          <t>01:42:05</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00:21:20</t>
+          <t>02:00:05</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -668,12 +656,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>00:03:20</t>
+          <t>01:42:05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>00:21:20</t>
+          <t>02:00:05</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -696,12 +684,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>00:03:20</t>
+          <t>01:42:05</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>00:21:20</t>
+          <t>02:00:05</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -724,12 +712,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>00:21:20</t>
+          <t>21:00:45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>05:21:20</t>
+          <t>26:00:45</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -747,17 +735,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>工业清洗机1-1</t>
+          <t>工业清洗机1-5</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>00:21:20</t>
+          <t>21:00:45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>02:21:20</t>
+          <t>23:00:45</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -780,12 +768,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>05:21:20</t>
+          <t>30:25:40</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>10:21:20</t>
+          <t>35:25:40</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -803,21 +791,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>工业清洗机1-2</t>
+          <t>工业清洗机1-1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>00:05:10</t>
+          <t>03:42:30</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>00:23:10</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1080</v>
+        <v>864</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -831,21 +819,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>工业清洗机1-3</t>
+          <t>工业清洗机1-2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>00:05:10</t>
+          <t>03:42:30</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>00:23:10</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1080</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -859,21 +847,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>工业清洗机1-4</t>
+          <t>工业清洗机1-3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>00:05:10</t>
+          <t>03:42:30</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>00:23:10</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1080</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -887,21 +875,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>工业清洗机1-5</t>
+          <t>工业清洗机1-4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>00:05:10</t>
+          <t>03:42:30</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>00:23:10</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1080</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -915,25 +903,25 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>精密灌装机1-1</t>
+          <t>工业清洗机1-5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>00:29:50</t>
+          <t>03:42:30</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>01:59:50</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5400</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
     </row>
@@ -943,17 +931,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>精密灌装机1-2</t>
+          <t>精密灌装机1-1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>00:29:50</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>01:59:50</t>
+          <t>05:26:54</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -971,17 +959,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>精密灌装机1-3</t>
+          <t>精密灌装机1-2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>00:29:50</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>01:59:50</t>
+          <t>05:26:54</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -999,17 +987,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>精密灌装机1-4</t>
+          <t>精密灌装机1-3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>00:29:50</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>01:59:50</t>
+          <t>05:26:54</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1027,17 +1015,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>精密灌装机1-5</t>
+          <t>精密灌装机1-4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>00:29:50</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>01:59:50</t>
+          <t>05:26:54</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1055,21 +1043,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>自动化输送臂1-1</t>
+          <t>精密灌装机1-5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>00:29:50</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>01:44:50</t>
+          <t>05:26:54</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4500</v>
+        <v>5400</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1083,17 +1071,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>自动化输送臂1-2</t>
+          <t>自动化输送臂1-1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>00:29:50</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>01:44:50</t>
+          <t>05:11:54</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1111,17 +1099,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>自动化输送臂1-3</t>
+          <t>自动化输送臂1-2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>00:29:50</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>01:44:50</t>
+          <t>05:11:54</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1139,17 +1127,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>自动化输送臂1-4</t>
+          <t>自动化输送臂1-3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>00:29:50</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>01:44:50</t>
+          <t>05:11:54</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1167,25 +1155,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>精密灌装机1-1</t>
+          <t>自动化输送臂1-4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>01:59:50</t>
+          <t>03:56:54</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>02:12:11</t>
+          <t>05:11:54</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>741</v>
+        <v>4500</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B2</t>
         </is>
       </c>
     </row>
@@ -1195,17 +1183,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>精密灌装机1-2</t>
+          <t>精密灌装机1-1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>01:59:50</t>
+          <t>05:26:54</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>02:12:11</t>
+          <t>05:39:15</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1223,17 +1211,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>精密灌装机1-3</t>
+          <t>精密灌装机1-2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>01:59:50</t>
+          <t>05:26:54</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>02:12:11</t>
+          <t>05:39:15</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1251,17 +1239,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>精密灌装机1-4</t>
+          <t>精密灌装机1-3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>01:59:50</t>
+          <t>05:26:54</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>02:12:11</t>
+          <t>05:39:15</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1279,17 +1267,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>精密灌装机1-5</t>
+          <t>精密灌装机1-4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>01:59:50</t>
+          <t>05:26:54</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>02:12:11</t>
+          <t>05:39:15</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1307,25 +1295,25 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>高速抛光机1-1</t>
+          <t>精密灌装机1-5</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10:29:50</t>
+          <t>05:26:54</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>13:29:50</t>
+          <t>05:39:15</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10800</v>
+        <v>741</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
     </row>
@@ -1335,21 +1323,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>自动传感多功能机1-1</t>
+          <t>高速抛光机1-1</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10:29:50</t>
+          <t>26:41:10</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>14:05:50</t>
+          <t>29:41:10</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>12960</v>
+        <v>10800</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1363,25 +1351,25 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>工业清洗机1-2</t>
+          <t>自动传感多功能机1-1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01:54:00</t>
+          <t>26:41:10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>30:17:10</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2592</v>
+        <v>12960</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>B4</t>
         </is>
       </c>
     </row>
@@ -1391,17 +1379,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>工业清洗机1-3</t>
+          <t>工业清洗机1-1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01:54:00</t>
+          <t>00:03:50</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1419,17 +1407,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>工业清洗机1-4</t>
+          <t>工业清洗机1-2</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>01:54:00</t>
+          <t>00:03:50</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1447,17 +1435,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>工业清洗机1-5</t>
+          <t>工业清洗机1-3</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>01:54:00</t>
+          <t>00:03:50</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1475,17 +1463,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>自动化输送臂1-1</t>
+          <t>工业清洗机1-4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>01:54:00</t>
+          <t>00:03:50</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1503,17 +1491,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>自动化输送臂1-2</t>
+          <t>自动化输送臂1-1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>01:54:00</t>
+          <t>00:03:50</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1531,17 +1519,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>自动化输送臂1-3</t>
+          <t>自动化输送臂1-2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>01:54:00</t>
+          <t>00:03:50</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1559,17 +1547,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>自动化输送臂1-4</t>
+          <t>自动化输送臂1-3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>01:54:00</t>
+          <t>00:03:50</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -1587,25 +1575,25 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>精密灌装机1-1</t>
+          <t>自动化输送臂1-4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>00:03:50</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1482</v>
+        <v>2592</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
     </row>
@@ -1615,17 +1603,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>精密灌装机1-2</t>
+          <t>精密灌装机1-1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1643,17 +1631,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>精密灌装机1-3</t>
+          <t>精密灌装机1-2</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -1671,17 +1659,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>精密灌装机1-4</t>
+          <t>精密灌装机1-3</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1699,17 +1687,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>精密灌装机1-5</t>
+          <t>精密灌装机1-4</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>02:37:12</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1727,25 +1715,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>精密灌装机1-1</t>
+          <t>精密灌装机1-5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>00:47:02</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>03:23:30</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1296</v>
+        <v>1482</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
     </row>
@@ -1755,17 +1743,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>精密灌装机1-2</t>
+          <t>精密灌装机1-1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>03:23:30</t>
+          <t>01:33:20</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -1773,7 +1761,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C3#1</t>
         </is>
       </c>
     </row>
@@ -1783,17 +1771,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>精密灌装机1-3</t>
+          <t>精密灌装机1-2</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>03:23:30</t>
+          <t>01:33:20</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -1801,7 +1789,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C3#1</t>
         </is>
       </c>
     </row>
@@ -1811,17 +1799,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>精密灌装机1-4</t>
+          <t>精密灌装机1-3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>03:23:30</t>
+          <t>01:33:20</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -1829,7 +1817,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C3#1</t>
         </is>
       </c>
     </row>
@@ -1839,17 +1827,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>精密灌装机1-5</t>
+          <t>精密灌装机1-4</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>03:23:30</t>
+          <t>01:33:20</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -1857,7 +1845,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C3#1</t>
         </is>
       </c>
     </row>
@@ -1867,17 +1855,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>自动化输送臂1-1</t>
+          <t>精密灌装机1-5</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>03:23:30</t>
+          <t>01:33:20</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -1885,7 +1873,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C3#1</t>
         </is>
       </c>
     </row>
@@ -1895,17 +1883,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>自动化输送臂1-2</t>
+          <t>自动化输送臂1-1</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>03:23:30</t>
+          <t>01:33:20</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1913,7 +1901,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C3#1</t>
         </is>
       </c>
     </row>
@@ -1923,17 +1911,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>自动化输送臂1-3</t>
+          <t>自动化输送臂1-2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>03:23:30</t>
+          <t>01:33:20</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -1941,7 +1929,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C3#1</t>
         </is>
       </c>
     </row>
@@ -1951,17 +1939,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>自动化输送臂1-4</t>
+          <t>自动化输送臂1-3</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>03:01:54</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>03:23:30</t>
+          <t>01:33:20</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -1969,7 +1957,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C3#1</t>
         </is>
       </c>
     </row>
@@ -1979,25 +1967,25 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>高速抛光机1-1</t>
+          <t>自动化输送臂1-4</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>13:39:00</t>
+          <t>01:11:44</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>16:59:00</t>
+          <t>01:33:20</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>12000</v>
+        <v>1296</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3#1</t>
         </is>
       </c>
     </row>
@@ -2007,25 +1995,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>工业清洗机1-1</t>
+          <t>高速抛光机1-1</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>13:39:00</t>
+          <t>01:33:20</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>15:39:00</t>
+          <t>04:53:20</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>7200</v>
+        <v>12000</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C4#1</t>
         </is>
       </c>
     </row>
@@ -2035,17 +2023,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>工业清洗机1-2</t>
+          <t>工业清洗机1-1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>13:39:00</t>
+          <t>01:33:20</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>15:39:00</t>
+          <t>03:33:20</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2053,7 +2041,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C4#1</t>
         </is>
       </c>
     </row>
@@ -2063,25 +2051,25 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>自动传感多功能机1-1</t>
+          <t>工业清洗机1-2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>16:59:00</t>
+          <t>01:33:20</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>20:59:00</t>
+          <t>03:33:20</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>14400</v>
+        <v>7200</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4#1</t>
         </is>
       </c>
     </row>
@@ -2091,25 +2079,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>工业清洗机1-3</t>
+          <t>自动传感多功能机1-1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>02:41:32</t>
+          <t>10:02:00</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>03:29:32</t>
+          <t>14:02:00</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2880</v>
+        <v>14400</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C5#1</t>
         </is>
       </c>
     </row>
@@ -2119,25 +2107,25 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>工业清洗机1-4</t>
+          <t>精密灌装机1-1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>02:41:32</t>
+          <t>14:02:00</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>03:29:32</t>
+          <t>14:23:36</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2880</v>
+        <v>1296</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C3#2</t>
         </is>
       </c>
     </row>
@@ -2147,25 +2135,25 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>工业清洗机1-5</t>
+          <t>精密灌装机1-2</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>02:41:32</t>
+          <t>14:02:00</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>03:29:32</t>
+          <t>14:23:36</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2880</v>
+        <v>1296</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C3#2</t>
         </is>
       </c>
     </row>
@@ -2175,25 +2163,25 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>精密灌装机1-1</t>
+          <t>精密灌装机1-3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>03:29:32</t>
+          <t>14:02:00</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>04:17:32</t>
+          <t>14:23:36</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2880</v>
+        <v>1296</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C3#2</t>
         </is>
       </c>
     </row>
@@ -2203,25 +2191,25 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>精密灌装机1-2</t>
+          <t>精密灌装机1-4</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>03:29:32</t>
+          <t>14:02:00</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>04:17:32</t>
+          <t>14:23:36</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2880</v>
+        <v>1296</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C3#2</t>
         </is>
       </c>
     </row>
@@ -2231,25 +2219,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>精密灌装机1-3</t>
+          <t>精密灌装机1-5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>03:29:32</t>
+          <t>14:02:00</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>04:17:32</t>
+          <t>14:23:36</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2880</v>
+        <v>1296</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C3#2</t>
         </is>
       </c>
     </row>
@@ -2259,25 +2247,25 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>精密灌装机1-4</t>
+          <t>自动化输送臂1-1</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>03:29:32</t>
+          <t>14:02:00</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>04:17:32</t>
+          <t>14:23:36</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2880</v>
+        <v>1296</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C3#2</t>
         </is>
       </c>
     </row>
@@ -2287,25 +2275,25 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>精密灌装机1-5</t>
+          <t>自动化输送臂1-2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>03:29:32</t>
+          <t>14:02:00</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>04:17:32</t>
+          <t>14:23:36</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2880</v>
+        <v>1296</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C3#2</t>
         </is>
       </c>
     </row>
@@ -2315,25 +2303,25 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>自动化输送臂1-1</t>
+          <t>自动化输送臂1-3</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>03:29:32</t>
+          <t>14:02:00</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>04:09:32</t>
+          <t>14:23:36</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2400</v>
+        <v>1296</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C3#2</t>
         </is>
       </c>
     </row>
@@ -2343,25 +2331,25 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>自动化输送臂1-2</t>
+          <t>自动化输送臂1-4</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>03:29:32</t>
+          <t>14:02:00</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>04:09:32</t>
+          <t>14:23:36</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2400</v>
+        <v>1296</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C3#2</t>
         </is>
       </c>
     </row>
@@ -2371,25 +2359,25 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>自动化输送臂1-3</t>
+          <t>高速抛光机1-1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>03:29:32</t>
+          <t>17:32:00</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>04:09:32</t>
+          <t>20:52:00</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2400</v>
+        <v>12000</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C4#2</t>
         </is>
       </c>
     </row>
@@ -2399,25 +2387,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>自动化输送臂1-4</t>
+          <t>工业清洗机1-2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>03:29:32</t>
+          <t>17:32:00</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>04:09:32</t>
+          <t>19:32:00</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2400</v>
+        <v>7200</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C4#2</t>
         </is>
       </c>
     </row>
@@ -2427,25 +2415,25 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>精密灌装机1-1</t>
+          <t>工业清洗机1-3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>04:17:32</t>
+          <t>17:32:00</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>04:32:58</t>
+          <t>19:32:00</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>926</v>
+        <v>7200</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>C4#2</t>
         </is>
       </c>
     </row>
@@ -2455,25 +2443,25 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>精密灌装机1-2</t>
+          <t>自动传感多功能机1-1</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>04:17:32</t>
+          <t>22:32:00</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>04:32:58</t>
+          <t>26:32:00</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>926</v>
+        <v>14400</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>C5#2</t>
         </is>
       </c>
     </row>
@@ -2483,25 +2471,25 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>精密灌装机1-3</t>
+          <t>精密灌装机1-1</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>04:17:32</t>
+          <t>26:32:00</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>04:32:58</t>
+          <t>26:53:36</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>926</v>
+        <v>1296</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>C3#3</t>
         </is>
       </c>
     </row>
@@ -2511,25 +2499,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>精密灌装机1-4</t>
+          <t>精密灌装机1-2</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>04:17:32</t>
+          <t>26:32:00</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>04:32:58</t>
+          <t>26:53:36</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>926</v>
+        <v>1296</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>C3#3</t>
         </is>
       </c>
     </row>
@@ -2539,25 +2527,25 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>精密灌装机1-5</t>
+          <t>精密灌装机1-3</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>04:17:32</t>
+          <t>26:32:00</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>04:32:58</t>
+          <t>26:53:36</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>926</v>
+        <v>1296</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>C3#3</t>
         </is>
       </c>
     </row>
@@ -2567,25 +2555,25 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>高速抛光机1-1</t>
+          <t>精密灌装机1-4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>21:03:20</t>
+          <t>26:32:00</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>33:33:20</t>
+          <t>26:53:36</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>45000</v>
+        <v>1296</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>C3#3</t>
         </is>
       </c>
     </row>
@@ -2595,25 +2583,25 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>自动传感多功能机1-1</t>
+          <t>精密灌装机1-5</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>21:03:20</t>
+          <t>26:32:00</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>26:03:20</t>
+          <t>26:53:36</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>18000</v>
+        <v>1296</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>C3#3</t>
         </is>
       </c>
     </row>
@@ -2623,25 +2611,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>自动传感多功能机1-1</t>
+          <t>自动化输送臂1-1</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>33:33:20</t>
+          <t>26:32:00</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>38:33:20</t>
+          <t>26:53:36</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>18000</v>
+        <v>1296</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>C3#3</t>
         </is>
       </c>
     </row>
@@ -2651,25 +2639,25 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>高速抛光机1-1</t>
+          <t>自动化输送臂1-2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>38:33:20</t>
+          <t>26:32:00</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>45:33:20</t>
+          <t>26:53:36</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>25200</v>
+        <v>1296</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>C3#3</t>
         </is>
       </c>
     </row>
@@ -2679,25 +2667,25 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>工业清洗机1-3</t>
+          <t>自动化输送臂1-3</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>03:38:07</t>
+          <t>26:32:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>04:58:07</t>
+          <t>26:53:36</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4800</v>
+        <v>1296</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>C3#3</t>
         </is>
       </c>
     </row>
@@ -2707,25 +2695,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>工业清洗机1-4</t>
+          <t>自动化输送臂1-4</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>03:38:07</t>
+          <t>26:32:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>04:58:07</t>
+          <t>26:53:36</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4800</v>
+        <v>1296</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>C3#3</t>
         </is>
       </c>
     </row>
@@ -2735,25 +2723,25 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>工业清洗机1-5</t>
+          <t>高速抛光机1-1</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>03:38:07</t>
+          <t>29:50:20</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>04:58:07</t>
+          <t>33:10:20</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4800</v>
+        <v>12000</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>E1</t>
+          <t>C4#3</t>
         </is>
       </c>
     </row>
@@ -2763,25 +2751,25 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>精密灌装机1-1</t>
+          <t>工业清洗机1-1</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>04:58:07</t>
+          <t>29:50:20</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>05:18:42</t>
+          <t>31:50:20</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1235</v>
+        <v>7200</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>C4#3</t>
         </is>
       </c>
     </row>
@@ -2791,25 +2779,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>精密灌装机1-2</t>
+          <t>工业清洗机1-2</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>04:58:07</t>
+          <t>29:50:20</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>05:18:42</t>
+          <t>31:50:20</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1235</v>
+        <v>7200</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>C4#3</t>
         </is>
       </c>
     </row>
@@ -2819,25 +2807,25 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>精密灌装机1-3</t>
+          <t>自动传感多功能机1-1</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>04:58:07</t>
+          <t>35:34:25</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>05:18:42</t>
+          <t>39:34:25</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1235</v>
+        <v>14400</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>C5#3</t>
         </is>
       </c>
     </row>
@@ -2847,25 +2835,25 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>精密灌装机1-4</t>
+          <t>工业清洗机1-1</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>04:58:07</t>
+          <t>00:51:22</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>05:18:42</t>
+          <t>01:20:10</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1235</v>
+        <v>1728</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -2875,25 +2863,25 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>精密灌装机1-5</t>
+          <t>工业清洗机1-2</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>04:58:07</t>
+          <t>00:51:22</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>05:18:42</t>
+          <t>01:20:10</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1235</v>
+        <v>1728</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -2903,25 +2891,25 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>自动传感多功能机1-1</t>
+          <t>工业清洗机1-3</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>38:41:55</t>
+          <t>00:51:22</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>40:41:55</t>
+          <t>01:20:10</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>7200</v>
+        <v>1728</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -2931,25 +2919,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>工业清洗机1-3</t>
+          <t>工业清洗机1-4</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>38:41:55</t>
+          <t>00:51:22</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>40:41:55</t>
+          <t>01:20:10</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>7200</v>
+        <v>1728</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -2959,25 +2947,25 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>工业清洗机1-4</t>
+          <t>工业清洗机1-5</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>38:41:55</t>
+          <t>00:51:22</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>40:41:55</t>
+          <t>01:20:10</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>7200</v>
+        <v>1728</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>D1</t>
         </is>
       </c>
     </row>
@@ -2987,23 +2975,891 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>精密灌装机1-1</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>02:07:35</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>02:55:35</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>精密灌装机1-2</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>02:07:35</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>02:55:35</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>精密灌装机1-3</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>02:07:35</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>02:55:35</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>精密灌装机1-4</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>02:07:35</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>02:55:35</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>精密灌装机1-5</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>02:07:35</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>02:55:35</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>自动化输送臂1-1</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>02:07:35</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>02:47:35</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>自动化输送臂1-2</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>02:07:35</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>02:47:35</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>自动化输送臂1-3</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>02:07:35</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>02:47:35</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>自动化输送臂1-4</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>02:07:35</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>02:47:35</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2400</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>精密灌装机1-1</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>02:55:35</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>03:11:01</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>926</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>精密灌装机1-2</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>02:55:35</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>03:11:01</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>926</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>精密灌装机1-3</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>02:55:35</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>03:11:01</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>926</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>精密灌装机1-4</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>02:55:35</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>03:11:01</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>926</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>精密灌装机1-5</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>02:55:35</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>03:11:01</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>926</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>高速抛光机1-1</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>04:57:40</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>17:27:40</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>自动传感多功能机1-1</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>04:57:40</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>09:57:40</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>自动传感多功能机1-1</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>17:27:40</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>22:27:40</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>高速抛光机1-1</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>33:14:40</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>40:14:40</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>25200</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>工业清洗机1-1</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>04:02:54</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>04:50:54</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>工业清洗机1-2</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>04:02:54</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>04:50:54</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>工业清洗机1-3</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>04:02:54</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>04:50:54</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>工业清洗机1-4</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>04:02:54</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>04:50:54</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
           <t>工业清洗机1-5</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>38:41:55</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>40:41:55</t>
-        </is>
-      </c>
-      <c r="E92" t="n">
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>04:02:54</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>04:50:54</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>2880</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>精密灌装机1-1</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>05:45:15</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>06:05:50</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>1235</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>精密灌装机1-2</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>05:45:15</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>06:05:50</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>1235</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>精密灌装机1-3</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>05:45:15</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>06:05:50</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1235</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>精密灌装机1-4</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>05:45:15</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>06:05:50</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1235</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>精密灌装机1-5</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>05:45:15</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>06:05:50</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1235</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>自动传感多功能机1-1</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>14:09:05</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>16:09:05</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
         <v>7200</v>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>工业清洗机1-1</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>14:09:05</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>16:09:05</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>7200</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>工业清洗机1-2</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>14:09:05</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>16:09:05</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>7200</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>工业清洗机1-3</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>14:09:05</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>16:09:05</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>7200</v>
+      </c>
+      <c r="F123" t="inlineStr">
         <is>
           <t>E3</t>
         </is>
@@ -3024,7 +3880,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>完成问题2任务的最短时长(s)</t>
         </is>
@@ -3032,7 +3888,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>164000</v>
+        <v>144880</v>
       </c>
     </row>
   </sheetData>
